--- a/data/trans_bre/IP16A98-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 9,15</t>
+          <t>-33,71; 8,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-25,68; 31,13</t>
+          <t>-22,66; 31,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 74,65</t>
+          <t>-7,13; 74,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-85,78; 90,49</t>
+          <t>-86,24; 101,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-85,49; —</t>
+          <t>-77,36; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,64; —</t>
+          <t>-47,5; —</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 7,07</t>
+          <t>-9,38; 7,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 5,96</t>
+          <t>-14,16; 5,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 3,57</t>
+          <t>-19,02; 4,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 71,93</t>
+          <t>-49,86; 75,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,43; 36,19</t>
+          <t>-55,03; 33,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,09; 22,14</t>
+          <t>-70,31; 26,4</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 6,26</t>
+          <t>-17,64; 5,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,46; 10,15</t>
+          <t>-20,99; 9,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 18,09</t>
+          <t>-9,6; 18,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-87,55; 134,32</t>
+          <t>-89,14; 78,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,15; 127,25</t>
+          <t>-78,0; 111,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-48,46; 290,73</t>
+          <t>-47,05; 303,86</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 3,51</t>
+          <t>-9,76; 3,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 4,18</t>
+          <t>-11,55; 3,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 9,54</t>
+          <t>-10,16; 10,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,93; 31,75</t>
+          <t>-52,47; 30,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 26,03</t>
+          <t>-45,9; 24,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,2; 64,24</t>
+          <t>-45,17; 72,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-33,71; 8,77</t>
+          <t>-30,62; 9,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 31,14</t>
+          <t>-23,56; 31,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 74,31</t>
+          <t>-5,86; 77,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-86,24; 101,48</t>
+          <t>-83,73; 94,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,36; —</t>
+          <t>-89,95; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,5; —</t>
+          <t>-38,57; —</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 7,56</t>
+          <t>-9,3; 6,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 5,45</t>
+          <t>-13,74; 6,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 4,25</t>
+          <t>-19,29; 4,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 75,6</t>
+          <t>-50,7; 70,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,03; 33,02</t>
+          <t>-53,62; 39,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,31; 26,4</t>
+          <t>-72,39; 26,96</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 5,28</t>
+          <t>-17,92; 5,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-20,99; 9,28</t>
+          <t>-21,07; 9,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 18,15</t>
+          <t>-9,24; 18,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-89,14; 78,17</t>
+          <t>-87,13; 96,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,0; 111,37</t>
+          <t>-76,82; 123,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 303,86</t>
+          <t>-52,06; 295,2</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 3,44</t>
+          <t>-9,87; 3,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,55; 3,97</t>
+          <t>-11,43; 4,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 10,82</t>
+          <t>-11,78; 9,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 30,8</t>
+          <t>-51,33; 29,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 24,54</t>
+          <t>-45,24; 32,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 72,56</t>
+          <t>-49,8; 63,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Estudios-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han  consumido otros medicamentos</t>
+          <t>Menores que consumieron otros medicamentos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33,31</t>
+          <t>6,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>193,26%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,62; 9,09</t>
+          <t>-32,88; 9,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 31,85</t>
+          <t>-25,68; 31,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 77,09</t>
+          <t>-18,88; 38,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-83,73; 94,82</t>
+          <t>-85,78; 90,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-89,95; —</t>
+          <t>-85,49; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-38,57; —</t>
+          <t>-81,35; 675,75</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-5,95</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-29,26%</t>
+          <t>-4,84%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 6,78</t>
+          <t>-9,37; 7,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,74; 6,12</t>
+          <t>-14,1; 5,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 4,08</t>
+          <t>-14,6; 8,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 70,1</t>
+          <t>-51,33; 71,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,62; 39,24</t>
+          <t>-54,43; 36,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,39; 26,96</t>
+          <t>-52,92; 52,49</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,62</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 5,26</t>
+          <t>-17,33; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 9,78</t>
+          <t>-21,46; 10,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 18,29</t>
+          <t>-10,99; 19,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-87,13; 96,26</t>
+          <t>-87,55; 134,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-76,82; 123,24</t>
+          <t>-80,15; 127,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,06; 295,2</t>
+          <t>-50,21; 288,06</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 3,15</t>
+          <t>-9,31; 3,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 4,8</t>
+          <t>-12,21; 4,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 9,51</t>
+          <t>-8,81; 8,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 29,91</t>
+          <t>-50,93; 31,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 32,38</t>
+          <t>-49,56; 26,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,8; 63,97</t>
+          <t>-37,61; 58,71</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A98-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16A98-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,6 +524,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -531,43 +542,55 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -582,6 +605,8 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -594,239 +619,189 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-10,26</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,37</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,55</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-41,72%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>39,96%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.536610392957124</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.345115392340728</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.856628059535162</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.8098316784074397</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.276459444139434</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.888253900660641</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1812616832432066</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-32,88; 9,15</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-25,68; 31,13</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-18,88; 38,51</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-85,78; 90,49</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-85,49; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-81,35; 675,75</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.435526038627173</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.544304421321572</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-1.174435590958518</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-5.850380138001459</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="n">
+        <v>-0.8216409494739723</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.7411590572351273</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.8727999810117127</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.870485378605944</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.936797938210516</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.233669511908923</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="n">
+        <v>2.14527821874237</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>5.144411431524243</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,01</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-4,27</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,96</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-7,07%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-19,85%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-4,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-9,37; 7,07</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-14,1; 5,96</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-14,6; 8,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-51,33; 71,93</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-54,43; 36,19</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-52,92; 52,49</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.1237415095770465</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.3476700029893892</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.7396055480942628</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.4541187093903075</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.4450790939930838</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.120255435049791</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.1962130371955851</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1004193043949372</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,61</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-4,69</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,77</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-41,88%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-25,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,81%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.5544851051367563</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.071750050322291</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.561523898361914</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.327845393279804</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="n">
+        <v>-0.5581023601970364</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5519227958916599</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.521096997702074</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-17,33; 6,26</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-21,46; 10,15</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-10,99; 19,27</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-87,55; 134,32</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-80,15; 127,25</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-50,21; 288,06</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.4660561437799735</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.447319257652743</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.194134263368159</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.959859402375299</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="n">
+        <v>0.7195221605640189</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.418909159180414</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.5947398058613727</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,77 +809,183 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-3,11</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,32</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-20,45%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-16,33%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.32759132298362</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.5522370941701549</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.496589787155147</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="n">
+        <v>-0.4418285096022347</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.1983169743347891</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.4017051468565878</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-9,31; 3,51</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-12,21; 4,18</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-8,81; 8,33</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-50,93; 31,75</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-49,56; 26,03</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-37,61; 58,71</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>-4.364205547719375</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.315070962947365</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.051445148726475</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-0.9110353712606173</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7748147306221459</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5821512081813209</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>1.19805429358668</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.038134029282537</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.197675424933834</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="n">
+        <v>1.234684476540022</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.632865776827868</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.651671367873778</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.2742560723051189</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.6742004140364858</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.2862626670039708</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.1062068260108406</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.744214764697964</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.214638114932687</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.0851358743937965</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.02454967119310133</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.7318985772502838</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.045295309163318</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-1.798007706109021</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.282466232553192</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="n">
+        <v>-0.5169522063595375</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4405694074125874</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.4078642818350524</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.09778242182575554</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.763218123905832</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.154712266141316</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.049790930966696</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>0.3129420242584282</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.4380421475230336</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.6531988263963537</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -912,13 +993,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
